--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N88_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N88_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80.19094415371356</v>
+        <v>13.03102842497845</v>
       </c>
       <c r="D2" t="n">
-        <v>80.04926018260458</v>
+        <v>13.00800477967324</v>
       </c>
       <c r="E2" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F2" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.02613180235267</v>
+        <v>1.954246417882308</v>
       </c>
       <c r="D3" t="n">
-        <v>4.701816053636074</v>
+        <v>0.7640451087158621</v>
       </c>
       <c r="E3" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F3" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.49706722738929</v>
+        <v>10.48077342445076</v>
       </c>
       <c r="D4" t="n">
-        <v>64.54175687235669</v>
+        <v>10.48803549175796</v>
       </c>
       <c r="E4" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F4" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.80267741421105</v>
+        <v>5.817935079809296</v>
       </c>
       <c r="D5" t="n">
-        <v>32.0624390837628</v>
+        <v>5.210146351111455</v>
       </c>
       <c r="E5" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F5" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.00079108680543</v>
+        <v>8.937628551605883</v>
       </c>
       <c r="D6" t="n">
-        <v>55.35962815231637</v>
+        <v>8.995939574751411</v>
       </c>
       <c r="E6" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F6" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.803944860285164</v>
+        <v>0.9431410397963392</v>
       </c>
       <c r="D7" t="n">
-        <v>5.902211251281016</v>
+        <v>0.9591093283331651</v>
       </c>
       <c r="E7" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F7" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.3555502205465</v>
+        <v>7.532776910838807</v>
       </c>
       <c r="D8" t="n">
-        <v>46.78167797879365</v>
+        <v>7.602022671553968</v>
       </c>
       <c r="E8" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F8" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.17973812733136</v>
+        <v>2.629207445691347</v>
       </c>
       <c r="D9" t="n">
-        <v>16.95273417637797</v>
+        <v>2.754819303661419</v>
       </c>
       <c r="E9" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F9" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.13658228429264</v>
+        <v>2.947194621197554</v>
       </c>
       <c r="D10" t="n">
-        <v>14.14526829126602</v>
+        <v>2.298606097330729</v>
       </c>
       <c r="E10" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F10" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.5251523238542</v>
+        <v>4.310337252626308</v>
       </c>
       <c r="D11" t="n">
-        <v>28.091218927025</v>
+        <v>4.564823075641563</v>
       </c>
       <c r="E11" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F11" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.44349617996118</v>
+        <v>2.672068129243693</v>
       </c>
       <c r="D12" t="n">
-        <v>18.79578470132567</v>
+        <v>3.054315013965422</v>
       </c>
       <c r="E12" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F12" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.49525905239192</v>
+        <v>5.930479596013687</v>
       </c>
       <c r="D13" t="n">
-        <v>7.014582708583714</v>
+        <v>1.139869690144854</v>
       </c>
       <c r="E13" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F13" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.32231603842978</v>
+        <v>6.552376356244839</v>
       </c>
       <c r="D14" t="n">
-        <v>17.28953599105795</v>
+        <v>2.809549598546917</v>
       </c>
       <c r="E14" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F14" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.91682231909424</v>
+        <v>6.648983626852815</v>
       </c>
       <c r="D15" t="n">
-        <v>7.754564576810949</v>
+        <v>1.260116743731779</v>
       </c>
       <c r="E15" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F15" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.77304333966444</v>
+        <v>5.163119542695472</v>
       </c>
       <c r="D16" t="n">
-        <v>8.905841885996443</v>
+        <v>1.447199306474422</v>
       </c>
       <c r="E16" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F16" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.0311181147894</v>
+        <v>4.230056693653278</v>
       </c>
       <c r="D17" t="n">
-        <v>27.14888358021021</v>
+        <v>4.411693581784159</v>
       </c>
       <c r="E17" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F17" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>58.92901569171656</v>
+        <v>9.575965049903942</v>
       </c>
       <c r="D18" t="n">
-        <v>56.27901814915958</v>
+        <v>9.145340449238432</v>
       </c>
       <c r="E18" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F18" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>9.432847545322607</v>
+        <v>1.532837726114924</v>
       </c>
       <c r="D19" t="n">
-        <v>8.839133004822646</v>
+        <v>1.43635911328368</v>
       </c>
       <c r="E19" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F19" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>72.36914364366667</v>
+        <v>11.75998584209584</v>
       </c>
       <c r="D20" t="n">
-        <v>69.85652212542506</v>
+        <v>11.35168484538157</v>
       </c>
       <c r="E20" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F20" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>34.77337919430212</v>
+        <v>5.650674119074094</v>
       </c>
       <c r="D21" t="n">
-        <v>34.22175653729819</v>
+        <v>5.561035437310956</v>
       </c>
       <c r="E21" t="n">
-        <v>20.75676770133447</v>
+        <v>3.372974751466851</v>
       </c>
       <c r="F21" t="n">
-        <v>23.21637766593959</v>
+        <v>3.772661370715182</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
